--- a/catalogos/CATALOGO_LINEAS_VALIDAS_17082026.xlsx
+++ b/catalogos/CATALOGO_LINEAS_VALIDAS_17082026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.lopez\Documents\CONAVI_P\VALIDADORES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.lopez\Documents\CONAVI_P\VALIDADORES\validador\catalogos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9492" tabRatio="635" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12570" tabRatio="635" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Adquisición" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="41">
   <si>
     <t>Autoproducción</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>Adquisición</t>
-  </si>
-  <si>
-    <t>Reubicación</t>
   </si>
   <si>
     <t>Reconstrucción</t>
@@ -126,9 +123,6 @@
     <t>Trámites legales</t>
   </si>
   <si>
-    <t>Subsidio 100%</t>
-  </si>
-  <si>
     <t>Espacio auxiliar productivo</t>
   </si>
   <si>
@@ -153,9 +147,6 @@
     <t>Cofinanciamiento sin crédito</t>
   </si>
   <si>
-    <t>subsidio 100%</t>
-  </si>
-  <si>
     <t>Vivienda para el Bienestar</t>
   </si>
   <si>
@@ -170,6 +161,12 @@
   <si>
     <t xml:space="preserve">Cofinanciamiento sin crédito
 </t>
+  </si>
+  <si>
+    <t>Reubicación de vivienda</t>
+  </si>
+  <si>
+    <t>Subsidio 100% CONAVI</t>
   </si>
 </sst>
 </file>
@@ -450,6 +447,960 @@
   </cellStyles>
   <dxfs count="56">
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -487,47 +1438,207 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -592,393 +1703,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1049,6 +1774,64 @@
         <name val="Noto Sans"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="none">
@@ -1056,7 +1839,124 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Noto Sans"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1151,67 +2051,14 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <border outline="0">
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1247,856 +2094,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Noto Sans"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2112,7 +2109,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabla4" displayName="Tabla4" ref="A1:F14" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54" tableBorderDxfId="53">
-  <autoFilter ref="A1:F14"/>
   <tableColumns count="6">
     <tableColumn id="1" name="esquema" dataDxfId="52"/>
     <tableColumn id="2" name="modalidad" dataDxfId="51"/>
@@ -2127,18 +2123,6 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabla3" displayName="Tabla3" ref="A1:F64" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="A1:F64">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Subsidio 100%"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Mejoramiento de vivienda"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="6">
     <tableColumn id="1" name="esquema" dataDxfId="44"/>
     <tableColumn id="2" name="modalidad" dataDxfId="43"/>
@@ -2153,59 +2137,55 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:F29" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
-  <autoFilter ref="A1:F29"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="esquema" dataDxfId="0"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="33"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="32"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="31"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="30"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="29"/>
+    <tableColumn id="1" name="esquema" dataDxfId="33"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="32"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="31"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="30"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="29"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:F35" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
-  <autoFilter ref="A1:F35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:F35" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <tableColumns count="6">
-    <tableColumn id="1" name="esquema" dataDxfId="26"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="25"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="24"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="23"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="22"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="21"/>
+    <tableColumn id="1" name="esquema" dataDxfId="25"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="24"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="23"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="22"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="21"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:F2" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
-  <autoFilter ref="A1:F2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabla5" displayName="Tabla5" ref="A1:F2" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <tableColumns count="6">
-    <tableColumn id="1" name="esquema" dataDxfId="16"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="15"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="14"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="13"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="12"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="11"/>
+    <tableColumn id="1" name="esquema" dataDxfId="15"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="14"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="13"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="12"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="11"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:F3" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:F3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabla6" displayName="Tabla6" ref="A1:F3" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <tableColumns count="6">
-    <tableColumn id="1" name="esquema" dataDxfId="6"/>
-    <tableColumn id="2" name="modalidad" dataDxfId="5"/>
-    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="4"/>
-    <tableColumn id="4" name="uma_la" dataDxfId="3"/>
-    <tableColumn id="5" name="linea_complementaria" dataDxfId="2"/>
-    <tableColumn id="6" name="uma_lc" dataDxfId="1"/>
+    <tableColumn id="1" name="esquema" dataDxfId="5"/>
+    <tableColumn id="2" name="modalidad" dataDxfId="4"/>
+    <tableColumn id="3" name="linea_de_apoyo" dataDxfId="3"/>
+    <tableColumn id="4" name="uma_la" dataDxfId="2"/>
+    <tableColumn id="5" name="linea_complementaria" dataDxfId="1"/>
+    <tableColumn id="6" name="uma_lc" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2418,46 +2398,46 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.59765625" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.69921875" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69921875" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.59765625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="1" width="27.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="D1" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="F1" s="31" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="16">
         <v>190</v>
@@ -2465,15 +2445,15 @@
       <c r="E2" s="30"/>
       <c r="F2" s="29"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="16">
         <v>170</v>
@@ -2481,15 +2461,15 @@
       <c r="E3" s="30"/>
       <c r="F3" s="29"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="16">
         <v>30</v>
@@ -2497,15 +2477,15 @@
       <c r="E4" s="30"/>
       <c r="F4" s="29"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="16">
         <v>140</v>
@@ -2513,7 +2493,7 @@
       <c r="E5" s="30"/>
       <c r="F5" s="29"/>
     </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="19" t="s">
         <v>11</v>
       </c>
@@ -2521,7 +2501,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="16">
         <v>140</v>
@@ -2533,7 +2513,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
@@ -2541,7 +2521,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="16">
         <v>140</v>
@@ -2553,7 +2533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
@@ -2561,19 +2541,19 @@
         <v>12</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="16">
         <v>140</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="16">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
@@ -2581,19 +2561,19 @@
         <v>12</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="16">
         <v>140</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
@@ -2601,7 +2581,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="16">
         <v>140</v>
@@ -2613,7 +2593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
         <v>11</v>
       </c>
@@ -2621,7 +2601,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="16">
         <v>140</v>
@@ -2633,7 +2613,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="19" t="s">
         <v>11</v>
       </c>
@@ -2641,7 +2621,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="16">
         <v>140</v>
@@ -2653,7 +2633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
@@ -2661,19 +2641,19 @@
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="16">
         <v>140</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="16">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="19" t="s">
         <v>11</v>
       </c>
@@ -2681,13 +2661,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="16">
         <v>140</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="16">
         <v>16</v>
@@ -2708,40 +2688,40 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:F64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.59765625" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" style="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.09765625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.8984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.69921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="1"/>
+    <col min="3" max="3" width="68.109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="F1" s="28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>0</v>
@@ -2759,9 +2739,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>0</v>
@@ -2779,9 +2759,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>0</v>
@@ -2799,9 +2779,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>0</v>
@@ -2819,9 +2799,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>0</v>
@@ -2839,9 +2819,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>0</v>
@@ -2859,9 +2839,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>0</v>
@@ -2879,9 +2859,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -2899,9 +2879,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>0</v>
@@ -2919,9 +2899,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>0</v>
@@ -2939,9 +2919,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>0</v>
@@ -2959,9 +2939,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>0</v>
@@ -2979,9 +2959,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>0</v>
@@ -2999,9 +2979,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>0</v>
@@ -3019,9 +2999,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>0</v>
@@ -3039,9 +3019,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>0</v>
@@ -3059,9 +3039,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>0</v>
@@ -3079,9 +3059,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>0</v>
@@ -3099,9 +3079,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>0</v>
@@ -3119,9 +3099,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>0</v>
@@ -3139,9 +3119,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>0</v>
@@ -3159,9 +3139,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>0</v>
@@ -3179,9 +3159,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>0</v>
@@ -3199,9 +3179,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>0</v>
@@ -3219,9 +3199,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>0</v>
@@ -3239,9 +3219,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>0</v>
@@ -3259,9 +3239,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>0</v>
@@ -3279,9 +3259,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>0</v>
@@ -3299,9 +3279,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>0</v>
@@ -3319,9 +3299,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>0</v>
@@ -3339,9 +3319,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>0</v>
@@ -3359,9 +3339,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>0</v>
@@ -3379,9 +3359,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>0</v>
@@ -3399,9 +3379,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>0</v>
@@ -3419,9 +3399,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>0</v>
@@ -3439,9 +3419,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>0</v>
@@ -3459,9 +3439,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>0</v>
@@ -3479,9 +3459,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>0</v>
@@ -3499,9 +3479,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>0</v>
@@ -3519,9 +3499,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>0</v>
@@ -3539,9 +3519,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>0</v>
@@ -3559,9 +3539,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>0</v>
@@ -3579,9 +3559,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>0</v>
@@ -3599,9 +3579,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>0</v>
@@ -3619,9 +3599,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>0</v>
@@ -3639,9 +3619,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>0</v>
@@ -3659,9 +3639,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>0</v>
@@ -3679,9 +3659,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>0</v>
@@ -3699,9 +3679,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>0</v>
@@ -3719,9 +3699,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>0</v>
@@ -3739,9 +3719,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>0</v>
@@ -3759,9 +3739,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>0</v>
@@ -3779,9 +3759,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>0</v>
@@ -3799,9 +3779,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>0</v>
@@ -3819,9 +3799,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>0</v>
@@ -3839,9 +3819,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>0</v>
@@ -3859,9 +3839,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>0</v>
@@ -3879,9 +3859,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>0</v>
@@ -3899,9 +3879,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>0</v>
@@ -3919,9 +3899,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>0</v>
@@ -3939,9 +3919,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>0</v>
@@ -3959,9 +3939,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>0</v>
@@ -3979,9 +3959,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>0</v>
@@ -4014,46 +3994,46 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.5" style="27" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.796875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="1" width="29.44140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="D1" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="F1" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="26" t="s">
+      <c r="B2" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="11">
         <v>86</v>
@@ -4061,15 +4041,15 @@
       <c r="E2" s="18"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="11">
         <v>86</v>
@@ -4077,12 +4057,12 @@
       <c r="E3" s="18"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>9</v>
@@ -4097,12 +4077,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4117,12 +4097,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>9</v>
@@ -4137,12 +4117,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>9</v>
@@ -4157,15 +4137,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="11">
         <v>170</v>
@@ -4173,15 +4153,15 @@
       <c r="E8" s="19"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="11">
         <v>170</v>
@@ -4189,15 +4169,15 @@
       <c r="E9" s="19"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11">
         <v>140</v>
@@ -4205,15 +4185,15 @@
       <c r="E10" s="19"/>
       <c r="F10" s="14"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11">
         <v>140</v>
@@ -4221,15 +4201,15 @@
       <c r="E11" s="19"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="16">
         <v>140</v>
@@ -4241,15 +4221,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="16">
         <v>140</v>
@@ -4261,15 +4241,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="16">
         <v>140</v>
@@ -4281,15 +4261,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="16">
         <v>140</v>
@@ -4301,15 +4281,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="16">
         <v>140</v>
@@ -4321,35 +4301,35 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="16">
         <v>140</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="16">
         <v>140</v>
@@ -4361,15 +4341,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="16">
         <v>140</v>
@@ -4381,15 +4361,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="16">
         <v>140</v>
@@ -4401,15 +4381,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="16">
         <v>140</v>
@@ -4421,15 +4401,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="16">
         <v>140</v>
@@ -4441,35 +4421,35 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="16">
         <v>140</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="16">
         <v>140</v>
@@ -4481,15 +4461,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="16">
         <v>140</v>
@@ -4501,15 +4481,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="16">
         <v>140</v>
@@ -4521,15 +4501,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="16">
         <v>140</v>
@@ -4541,15 +4521,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" s="16">
         <v>140</v>
@@ -4561,21 +4541,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D29" s="17">
         <v>140</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" s="15">
         <v>90</v>
@@ -4596,46 +4576,46 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="27" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.19921875" style="27" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.796875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="27"/>
+    <col min="1" max="1" width="25.44140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.21875" style="27" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="F1" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="12" t="s">
-        <v>35</v>
-      </c>
       <c r="B2" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="16">
         <v>270</v>
@@ -4647,15 +4627,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="16">
         <v>270</v>
@@ -4667,15 +4647,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="16">
         <v>50</v>
@@ -4687,15 +4667,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="16">
         <v>50</v>
@@ -4707,15 +4687,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="16">
         <v>50</v>
@@ -4727,15 +4707,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="16">
         <v>50</v>
@@ -4747,15 +4727,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="16">
         <v>50</v>
@@ -4767,15 +4747,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="16">
         <v>50</v>
@@ -4787,15 +4767,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="16">
         <v>100</v>
@@ -4807,15 +4787,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="16">
         <v>100</v>
@@ -4827,15 +4807,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="16">
         <v>100</v>
@@ -4847,15 +4827,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="16">
         <v>100</v>
@@ -4867,15 +4847,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="16">
         <v>100</v>
@@ -4887,12 +4867,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>10</v>
@@ -4907,12 +4887,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>10</v>
@@ -4927,12 +4907,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>10</v>
@@ -4947,12 +4927,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>10</v>
@@ -4967,15 +4947,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="29">
         <v>270</v>
@@ -4987,15 +4967,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="29">
         <v>270</v>
@@ -5007,15 +4987,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="29">
         <v>50</v>
@@ -5027,15 +5007,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="29">
         <v>50</v>
@@ -5047,15 +5027,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="29">
         <v>50</v>
@@ -5067,15 +5047,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="29">
         <v>50</v>
@@ -5087,15 +5067,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" s="29">
         <v>50</v>
@@ -5107,15 +5087,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26" s="29">
         <v>50</v>
@@ -5127,15 +5107,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" s="29">
         <v>100</v>
@@ -5147,15 +5127,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="29">
         <v>100</v>
@@ -5167,15 +5147,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="29">
         <v>100</v>
@@ -5187,15 +5167,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" s="29">
         <v>100</v>
@@ -5207,15 +5187,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="29">
         <v>100</v>
@@ -5227,12 +5207,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>10</v>
@@ -5247,12 +5227,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>10</v>
@@ -5267,12 +5247,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>10</v>
@@ -5287,12 +5267,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="19" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>10</v>
@@ -5321,46 +5301,46 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.19921875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="1"/>
+    <col min="3" max="3" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="F1" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="4">
         <v>25</v>
@@ -5382,46 +5362,46 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.3984375" style="1"/>
+    <col min="1" max="1" width="25.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="F1" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="16">
         <v>4</v>
@@ -5433,15 +5413,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="39">
         <v>4</v>
